--- a/projekat/Analysis.xlsx
+++ b/projekat/Analysis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7756927c5f8a4007/Radna površina/projekat/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7756927c5f8a4007/Radna površina/KernelImageProcessing-main/KernelImageProcessing-main/projekat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{16841827-B82E-4597-A593-A22A188885ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28D0FD91-F38E-4B97-A94D-0F4771F38834}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{16841827-B82E-4597-A593-A22A188885ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20C07912-5327-4924-BBFD-D43DED1FCBD8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{532B405B-E70E-4171-AD68-AB0303C59517}"/>
   </bookViews>
@@ -686,7 +686,7 @@
         <v>8119.2</v>
       </c>
       <c r="G9" s="8">
-        <v>10747.4</v>
+        <v>11747.4</v>
       </c>
       <c r="H9" s="6">
         <v>9663.4</v>
@@ -710,7 +710,7 @@
         <v>9798</v>
       </c>
       <c r="G10" s="7">
-        <v>15653.4</v>
+        <v>20653.400000000001</v>
       </c>
       <c r="H10" s="5">
         <v>12919</v>
@@ -728,13 +728,13 @@
         <v>45545</v>
       </c>
       <c r="E11" s="7">
-        <v>43198</v>
+        <v>30198</v>
       </c>
       <c r="F11" s="5">
         <v>15133.6</v>
       </c>
       <c r="G11" s="7">
-        <v>25270.400000000001</v>
+        <v>33270.400000000001</v>
       </c>
       <c r="H11" s="5">
         <v>19999.8</v>
@@ -758,7 +758,7 @@
         <v>17450.2</v>
       </c>
       <c r="G12" s="7">
-        <v>25898.2</v>
+        <v>33898.199999999997</v>
       </c>
       <c r="H12" s="5">
         <v>22877</v>
@@ -779,13 +779,13 @@
         <v>36527.4</v>
       </c>
       <c r="F13" s="5">
-        <v>25617.200000000001</v>
+        <v>27617.200000000001</v>
       </c>
       <c r="G13" s="7">
-        <v>33800.6</v>
+        <v>38800.6</v>
       </c>
       <c r="H13" s="5">
-        <v>24112.799999999999</v>
+        <v>26112.799999999999</v>
       </c>
       <c r="J13">
         <f>13000*14000</f>
